--- a/impact_v2.xlsx
+++ b/impact_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1B459D-2E05-4D16-85AA-C1E7261E99E2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7E26AF-1790-4B3C-B869-8C813818BE52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -219,37 +219,50 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="LCIA_AD-f"/>
+      <sheetName val="IW+f"/>
+      <sheetName val="LCIA_AD-e"/>
+      <sheetName val="LCI_AD-e"/>
+      <sheetName val="LCI_AD-f"/>
+      <sheetName val="LCIA_AD-d"/>
       <sheetName val="Waste_characteristics"/>
+      <sheetName val="Parameters"/>
       <sheetName val="LCI"/>
-      <sheetName val="LCI_AD-c"/>
       <sheetName val="LCI_AD-d"/>
+      <sheetName val="LCI_AD-a"/>
       <sheetName val="LCI_AD-b"/>
       <sheetName val="params_HC"/>
+      <sheetName val="LCIA_HC"/>
       <sheetName val="LCI_HC"/>
-      <sheetName val="LCIA_HC"/>
+      <sheetName val="LCIA_AD-a"/>
+      <sheetName val="LCIA_AD-b"/>
+      <sheetName val="LCI_AD-c"/>
+      <sheetName val="LCIA_AD-c"/>
       <sheetName val="LCI_IC"/>
       <sheetName val="LCIA_IC"/>
-      <sheetName val="LCI_AD-a"/>
-      <sheetName val="LCIA_AD-a"/>
-      <sheetName val="IW+f"/>
+      <sheetName val="IW+_end"/>
       <sheetName val="AD_a_end"/>
       <sheetName val="impact_process_end"/>
       <sheetName val="impact_process_mid"/>
-      <sheetName val="IW+_end"/>
       <sheetName val="IW+_mid"/>
-      <sheetName val="Parameters"/>
       <sheetName val="IC_end"/>
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13">
         <row r="70">
           <cell r="C70">
             <v>34.264521044421535</v>
@@ -259,8 +272,22 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15">
+        <row r="5">
+          <cell r="C5">
+            <v>130.89983518703079</v>
+          </cell>
+          <cell r="G5">
+            <v>15.5837763706547</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20">
         <row r="29">
           <cell r="C29">
             <v>35.421319139716672</v>
@@ -270,26 +297,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="5">
-          <cell r="C5">
-            <v>141.69101636421289</v>
-          </cell>
-          <cell r="G5">
-            <v>15.5837763706547</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -687,7 +701,7 @@
       </c>
       <c r="C7" s="4">
         <f>'[1]LCIA_AD-a'!$C$5</f>
-        <v>141.69101636421289</v>
+        <v>130.89983518703079</v>
       </c>
       <c r="D7" s="4">
         <f>'[1]LCIA_AD-a'!$G$5</f>
